--- a/丽水-漫展信息.xlsx
+++ b/丽水-漫展信息.xlsx
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -598,7 +598,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -644,7 +644,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>

--- a/丽水-漫展信息.xlsx
+++ b/丽水-漫展信息.xlsx
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -552,7 +552,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -598,7 +598,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -928,7 +928,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>

--- a/丽水-漫展信息.xlsx
+++ b/丽水-漫展信息.xlsx
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -552,7 +552,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -928,7 +928,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>

--- a/丽水-漫展信息.xlsx
+++ b/丽水-漫展信息.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -467,15 +467,10 @@
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>是否有舞台（字符串匹配）</t>
+          <t>Link</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
-        <is>
-          <t>Link</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
         <is>
           <t>Cover</t>
         </is>
@@ -506,22 +501,17 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>291</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="H2" t="b">
-        <v>0</v>
+        <v>302</v>
+      </c>
+      <c r="G2" t="n">
+        <v>45</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=78294</t>
+        </is>
       </c>
       <c r="I2" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78294</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
         <is>
           <t>//i1.hdslb.com/bfs/openplatform/202311/lP5IkqWn1699431829470.jpeg</t>
         </is>
@@ -552,22 +542,17 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>229</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="H3" t="b">
-        <v>0</v>
+        <v>234</v>
+      </c>
+      <c r="G3" t="n">
+        <v>50</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80714</t>
+        </is>
       </c>
       <c r="I3" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80714</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
         <is>
           <t>//i2.hdslb.com/bfs/openplatform/202401/rTvQio211704877379770.jpeg</t>
         </is>
@@ -598,22 +583,17 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>34</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="H4" t="b">
-        <v>0</v>
+        <v>43</v>
+      </c>
+      <c r="G4" t="n">
+        <v>45</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81032</t>
+        </is>
       </c>
       <c r="I4" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81032</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
         <is>
           <t>//i0.hdslb.com/bfs/openplatform/202401/LbqTNkvq1705561884633.png</t>
         </is>
@@ -644,22 +624,17 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>268</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="H5" t="b">
-        <v>0</v>
+        <v>270</v>
+      </c>
+      <c r="G5" t="n">
+        <v>45</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=79437</t>
+        </is>
       </c>
       <c r="I5" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79437</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
         <is>
           <t>//i1.hdslb.com/bfs/openplatform/202312/ee5hLUN61702276208812.jpeg</t>
         </is>
@@ -676,7 +651,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1"/>
+  <dimension ref="A1:I1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -715,15 +690,10 @@
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>是否有舞台（字符串匹配）</t>
+          <t>Link</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
-        <is>
-          <t>Link</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
         <is>
           <t>Cover</t>
         </is>
@@ -740,7 +710,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1"/>
+  <dimension ref="A1:I1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -779,15 +749,10 @@
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>是否有舞台（字符串匹配）</t>
+          <t>Link</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
-        <is>
-          <t>Link</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
         <is>
           <t>Cover</t>
         </is>
@@ -804,7 +769,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -843,15 +808,10 @@
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>是否有舞台（字符串匹配）</t>
+          <t>Link</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
-        <is>
-          <t>Link</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
         <is>
           <t>Cover</t>
         </is>
@@ -882,22 +842,17 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>291</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="H2" t="b">
-        <v>0</v>
+        <v>302</v>
+      </c>
+      <c r="G2" t="n">
+        <v>45</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=78294</t>
+        </is>
       </c>
       <c r="I2" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78294</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
         <is>
           <t>//i1.hdslb.com/bfs/openplatform/202311/lP5IkqWn1699431829470.jpeg</t>
         </is>
@@ -928,22 +883,17 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>229</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="H3" t="b">
-        <v>0</v>
+        <v>234</v>
+      </c>
+      <c r="G3" t="n">
+        <v>50</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80714</t>
+        </is>
       </c>
       <c r="I3" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80714</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
         <is>
           <t>//i2.hdslb.com/bfs/openplatform/202401/rTvQio211704877379770.jpeg</t>
         </is>
@@ -974,22 +924,17 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>34</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="H4" t="b">
-        <v>0</v>
+        <v>43</v>
+      </c>
+      <c r="G4" t="n">
+        <v>45</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81032</t>
+        </is>
       </c>
       <c r="I4" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81032</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
         <is>
           <t>//i0.hdslb.com/bfs/openplatform/202401/LbqTNkvq1705561884633.png</t>
         </is>
@@ -1020,22 +965,17 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>268</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="H5" t="b">
-        <v>0</v>
+        <v>270</v>
+      </c>
+      <c r="G5" t="n">
+        <v>45</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=79437</t>
+        </is>
       </c>
       <c r="I5" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79437</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
         <is>
           <t>//i1.hdslb.com/bfs/openplatform/202312/ee5hLUN61702276208812.jpeg</t>
         </is>

--- a/丽水-漫展信息.xlsx
+++ b/丽水-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="G2" t="n">
         <v>45</v>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="G3" t="n">
         <v>50</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="G4" t="n">
         <v>45</v>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="G5" t="n">
         <v>45</v>
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="G2" t="n">
         <v>45</v>
@@ -883,7 +883,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="G3" t="n">
         <v>50</v>
@@ -924,7 +924,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="G4" t="n">
         <v>45</v>
@@ -965,7 +965,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="G5" t="n">
         <v>45</v>

--- a/丽水-漫展信息.xlsx
+++ b/丽水-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="G2" t="n">
         <v>45</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G4" t="n">
         <v>45</v>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="G5" t="n">
         <v>45</v>
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="G2" t="n">
         <v>45</v>
@@ -924,7 +924,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G4" t="n">
         <v>45</v>
@@ -965,7 +965,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="G5" t="n">
         <v>45</v>

--- a/丽水-漫展信息.xlsx
+++ b/丽水-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="G2" t="n">
         <v>45</v>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="G3" t="n">
         <v>50</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G4" t="n">
         <v>45</v>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="G5" t="n">
         <v>45</v>
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="G2" t="n">
         <v>45</v>
@@ -883,7 +883,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="G3" t="n">
         <v>50</v>
@@ -924,7 +924,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G4" t="n">
         <v>45</v>
@@ -965,7 +965,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="G5" t="n">
         <v>45</v>

--- a/丽水-漫展信息.xlsx
+++ b/丽水-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="G2" t="n">
         <v>45</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="G4" t="n">
         <v>45</v>
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="G2" t="n">
         <v>45</v>
@@ -924,7 +924,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="G4" t="n">
         <v>45</v>

--- a/丽水-漫展信息.xlsx
+++ b/丽水-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="G2" t="n">
         <v>45</v>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="G3" t="n">
         <v>50</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G4" t="n">
         <v>45</v>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="G5" t="n">
         <v>45</v>
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="G2" t="n">
         <v>45</v>
@@ -883,7 +883,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="G3" t="n">
         <v>50</v>
@@ -924,7 +924,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G4" t="n">
         <v>45</v>
@@ -965,7 +965,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="G5" t="n">
         <v>45</v>

--- a/丽水-漫展信息.xlsx
+++ b/丽水-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="G2" t="n">
         <v>45</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G4" t="n">
         <v>45</v>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="G5" t="n">
         <v>45</v>
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="G2" t="n">
         <v>45</v>
@@ -924,7 +924,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G4" t="n">
         <v>45</v>
@@ -965,7 +965,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="G5" t="n">
         <v>45</v>

--- a/丽水-漫展信息.xlsx
+++ b/丽水-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="G2" t="n">
         <v>45</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G4" t="n">
         <v>45</v>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="G5" t="n">
         <v>45</v>
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="G2" t="n">
         <v>45</v>
@@ -924,7 +924,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G4" t="n">
         <v>45</v>
@@ -965,7 +965,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="G5" t="n">
         <v>45</v>

--- a/丽水-漫展信息.xlsx
+++ b/丽水-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="G2" t="n">
         <v>45</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G4" t="n">
         <v>45</v>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="G5" t="n">
         <v>45</v>
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="G2" t="n">
         <v>45</v>
@@ -924,7 +924,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G4" t="n">
         <v>45</v>
@@ -965,7 +965,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="G5" t="n">
         <v>45</v>

--- a/丽水-漫展信息.xlsx
+++ b/丽水-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>325</v>
+        <v>331</v>
       </c>
       <c r="G2" t="n">
         <v>45</v>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="G3" t="n">
         <v>50</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="G4" t="n">
         <v>45</v>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="G5" t="n">
         <v>45</v>
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>325</v>
+        <v>331</v>
       </c>
       <c r="G2" t="n">
         <v>45</v>
@@ -883,7 +883,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="G3" t="n">
         <v>50</v>
@@ -924,7 +924,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="G4" t="n">
         <v>45</v>
@@ -965,7 +965,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="G5" t="n">
         <v>45</v>

--- a/丽水-漫展信息.xlsx
+++ b/丽水-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="G2" t="n">
         <v>45</v>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="G3" t="n">
         <v>50</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="G4" t="n">
         <v>45</v>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="G5" t="n">
         <v>45</v>
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="G2" t="n">
         <v>45</v>
@@ -883,7 +883,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="G3" t="n">
         <v>50</v>
@@ -924,7 +924,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="G4" t="n">
         <v>45</v>
@@ -965,7 +965,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="G5" t="n">
         <v>45</v>

--- a/丽水-漫展信息.xlsx
+++ b/丽水-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="G2" t="n">
         <v>45</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="G4" t="n">
         <v>45</v>
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="G2" t="n">
         <v>45</v>
@@ -924,7 +924,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="G4" t="n">
         <v>45</v>

--- a/丽水-漫展信息.xlsx
+++ b/丽水-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="G2" t="n">
         <v>45</v>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="G3" t="n">
         <v>50</v>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="G5" t="n">
         <v>45</v>
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="G2" t="n">
         <v>45</v>
@@ -883,7 +883,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="G3" t="n">
         <v>50</v>
@@ -965,7 +965,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="G5" t="n">
         <v>45</v>

--- a/丽水-漫展信息.xlsx
+++ b/丽水-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="G2" t="n">
         <v>45</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G4" t="n">
         <v>45</v>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="G5" t="n">
         <v>45</v>
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="G2" t="n">
         <v>45</v>
@@ -924,7 +924,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G4" t="n">
         <v>45</v>
@@ -965,7 +965,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="G5" t="n">
         <v>45</v>

--- a/丽水-漫展信息.xlsx
+++ b/丽水-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="G2" t="n">
         <v>45</v>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="G5" t="n">
         <v>45</v>
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="G2" t="n">
         <v>45</v>
@@ -965,7 +965,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="G5" t="n">
         <v>45</v>

--- a/丽水-漫展信息.xlsx
+++ b/丽水-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="G2" t="n">
         <v>45</v>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="G5" t="n">
         <v>45</v>
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="G2" t="n">
         <v>45</v>
@@ -965,7 +965,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="G5" t="n">
         <v>45</v>

--- a/丽水-漫展信息.xlsx
+++ b/丽水-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="G2" t="n">
         <v>45</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G4" t="n">
         <v>45</v>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="G5" t="n">
         <v>45</v>
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="G2" t="n">
         <v>45</v>
@@ -924,7 +924,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G4" t="n">
         <v>45</v>
@@ -965,7 +965,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="G5" t="n">
         <v>45</v>

--- a/丽水-漫展信息.xlsx
+++ b/丽水-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>350</v>
+        <v>357</v>
       </c>
       <c r="G2" t="n">
         <v>45</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G4" t="n">
         <v>45</v>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="G5" t="n">
         <v>45</v>
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>350</v>
+        <v>357</v>
       </c>
       <c r="G2" t="n">
         <v>45</v>
@@ -924,7 +924,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G4" t="n">
         <v>45</v>
@@ -965,7 +965,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="G5" t="n">
         <v>45</v>

--- a/丽水-漫展信息.xlsx
+++ b/丽水-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="G2" t="n">
         <v>45</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="G4" t="n">
         <v>45</v>
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="G2" t="n">
         <v>45</v>
@@ -924,7 +924,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="G4" t="n">
         <v>45</v>

--- a/丽水-漫展信息.xlsx
+++ b/丽水-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>358</v>
+        <v>368</v>
       </c>
       <c r="G2" t="n">
         <v>45</v>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="G3" t="n">
         <v>50</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="G4" t="n">
         <v>45</v>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="G5" t="n">
         <v>45</v>
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>358</v>
+        <v>368</v>
       </c>
       <c r="G2" t="n">
         <v>45</v>
@@ -883,7 +883,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="G3" t="n">
         <v>50</v>
@@ -924,7 +924,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="G4" t="n">
         <v>45</v>
@@ -965,7 +965,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="G5" t="n">
         <v>45</v>

--- a/丽水-漫展信息.xlsx
+++ b/丽水-漫展信息.xlsx
@@ -501,10 +501,10 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="G2" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -545,7 +545,7 @@
         <v>243</v>
       </c>
       <c r="G3" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G4" t="n">
         <v>45</v>
@@ -842,10 +842,10 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="G2" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
         <v>243</v>
       </c>
       <c r="G3" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -924,7 +924,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G4" t="n">
         <v>45</v>

--- a/丽水-漫展信息.xlsx
+++ b/丽水-漫展信息.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -482,38 +482,38 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2024-02-07</t>
+          <t>2024-02-14</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>丽水·新年动漫狂欢盛典</t>
+          <t>丽水·YA●怀旧only</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>中东路848号(解放街交汇) 飞达国际大酒店</t>
+          <t>人民街567号 丽水体育中心</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2024.02.07 09:00-02.07 17:00</t>
+          <t>2024.02.14 09:00-02.14 17:00</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>370</v>
+        <v>89</v>
       </c>
       <c r="G2" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78294</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81032</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202311/lP5IkqWn1699431829470.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/LbqTNkvq1705561884633.png</t>
         </is>
       </c>
     </row>
@@ -523,118 +523,36 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2024-02-07</t>
+          <t>2024-02-18</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>龙泉·崩X铁X原ONLY</t>
+          <t>丽水·LPJ 现实X次元动漫展</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>金沙路26-1号 龙泉金沙温泉酒店</t>
+          <t>中东路848号(解放街交汇) 飞达国际大酒店</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2024.02.07 10:30-02.07 16:30</t>
+          <t>2024.02.18 10:00-02.18 17:00</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>243</v>
+        <v>302</v>
       </c>
       <c r="G3" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80714</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79437</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/rTvQio211704877379770.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2024-02-14</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>丽水·YA●怀旧only</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>人民街567号 丽水体育中心</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>2024.02.14 09:00-02.14 17:00</t>
-        </is>
-      </c>
-      <c r="F4" t="n">
-        <v>83</v>
-      </c>
-      <c r="G4" t="n">
-        <v>45</v>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81032</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/LbqTNkvq1705561884633.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2024-02-18</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>丽水·LPJ 现实X次元动漫展</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>中东路848号(解放街交汇) 飞达国际大酒店</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>2024.02.18 10:00-02.18 17:00</t>
-        </is>
-      </c>
-      <c r="F5" t="n">
-        <v>298</v>
-      </c>
-      <c r="G5" t="n">
-        <v>45</v>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79437</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
         <is>
           <t>//i1.hdslb.com/bfs/openplatform/202312/ee5hLUN61702276208812.jpeg</t>
         </is>
@@ -769,7 +687,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -823,38 +741,38 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2024-02-07</t>
+          <t>2024-02-14</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>丽水·新年动漫狂欢盛典</t>
+          <t>丽水·YA●怀旧only</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>中东路848号(解放街交汇) 飞达国际大酒店</t>
+          <t>人民街567号 丽水体育中心</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2024.02.07 09:00-02.07 17:00</t>
+          <t>2024.02.14 09:00-02.14 17:00</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>370</v>
+        <v>89</v>
       </c>
       <c r="G2" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78294</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81032</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202311/lP5IkqWn1699431829470.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/LbqTNkvq1705561884633.png</t>
         </is>
       </c>
     </row>
@@ -864,118 +782,36 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2024-02-07</t>
+          <t>2024-02-18</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>龙泉·崩X铁X原ONLY</t>
+          <t>丽水·LPJ 现实X次元动漫展</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>金沙路26-1号 龙泉金沙温泉酒店</t>
+          <t>中东路848号(解放街交汇) 飞达国际大酒店</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2024.02.07 10:30-02.07 16:30</t>
+          <t>2024.02.18 10:00-02.18 17:00</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>243</v>
+        <v>302</v>
       </c>
       <c r="G3" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80714</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79437</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/rTvQio211704877379770.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2024-02-14</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>丽水·YA●怀旧only</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>人民街567号 丽水体育中心</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>2024.02.14 09:00-02.14 17:00</t>
-        </is>
-      </c>
-      <c r="F4" t="n">
-        <v>83</v>
-      </c>
-      <c r="G4" t="n">
-        <v>45</v>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81032</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/LbqTNkvq1705561884633.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2024-02-18</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>丽水·LPJ 现实X次元动漫展</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>中东路848号(解放街交汇) 飞达国际大酒店</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>2024.02.18 10:00-02.18 17:00</t>
-        </is>
-      </c>
-      <c r="F5" t="n">
-        <v>298</v>
-      </c>
-      <c r="G5" t="n">
-        <v>45</v>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79437</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
         <is>
           <t>//i1.hdslb.com/bfs/openplatform/202312/ee5hLUN61702276208812.jpeg</t>
         </is>

--- a/丽水-漫展信息.xlsx
+++ b/丽水-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="G2" t="n">
         <v>45</v>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="G3" t="n">
         <v>45</v>
@@ -760,7 +760,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="G2" t="n">
         <v>45</v>
@@ -801,7 +801,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="G3" t="n">
         <v>45</v>

--- a/丽水-漫展信息.xlsx
+++ b/丽水-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="G2" t="n">
         <v>45</v>
@@ -760,7 +760,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="G2" t="n">
         <v>45</v>

--- a/丽水-漫展信息.xlsx
+++ b/丽水-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="G2" t="n">
         <v>45</v>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="G3" t="n">
         <v>45</v>
@@ -760,7 +760,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="G2" t="n">
         <v>45</v>
@@ -801,7 +801,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="G3" t="n">
         <v>45</v>

--- a/丽水-漫展信息.xlsx
+++ b/丽水-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="G2" t="n">
         <v>45</v>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="G3" t="n">
         <v>45</v>
@@ -760,7 +760,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="G2" t="n">
         <v>45</v>
@@ -801,7 +801,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="G3" t="n">
         <v>45</v>

--- a/丽水-漫展信息.xlsx
+++ b/丽水-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="G2" t="n">
         <v>45</v>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="G3" t="n">
         <v>45</v>
@@ -760,7 +760,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="G2" t="n">
         <v>45</v>
@@ -801,7 +801,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="G3" t="n">
         <v>45</v>

--- a/丽水-漫展信息.xlsx
+++ b/丽水-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="G2" t="n">
         <v>45</v>
@@ -760,7 +760,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="G2" t="n">
         <v>45</v>

--- a/丽水-漫展信息.xlsx
+++ b/丽水-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="G2" t="n">
         <v>45</v>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="G3" t="n">
         <v>45</v>
@@ -760,7 +760,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="G2" t="n">
         <v>45</v>
@@ -801,7 +801,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="G3" t="n">
         <v>45</v>

--- a/丽水-漫展信息.xlsx
+++ b/丽水-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="G2" t="n">
         <v>45</v>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="G3" t="n">
         <v>45</v>
@@ -760,7 +760,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="G2" t="n">
         <v>45</v>
@@ -801,7 +801,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="G3" t="n">
         <v>45</v>

--- a/丽水-漫展信息.xlsx
+++ b/丽水-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="G2" t="n">
         <v>45</v>
@@ -760,7 +760,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="G2" t="n">
         <v>45</v>

--- a/丽水-漫展信息.xlsx
+++ b/丽水-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="G2" t="n">
         <v>45</v>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="G3" t="n">
         <v>45</v>
@@ -760,7 +760,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="G2" t="n">
         <v>45</v>
@@ -801,7 +801,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="G3" t="n">
         <v>45</v>

--- a/丽水-漫展信息.xlsx
+++ b/丽水-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="G2" t="n">
         <v>45</v>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="G3" t="n">
         <v>45</v>
@@ -760,7 +760,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="G2" t="n">
         <v>45</v>
@@ -801,7 +801,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="G3" t="n">
         <v>45</v>

--- a/丽水-漫展信息.xlsx
+++ b/丽水-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="G2" t="n">
         <v>45</v>
@@ -528,7 +528,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>丽水·LPJ 现实X次元动漫展</t>
+          <t>丽水·LPJ 现实X次元动漫展（取消）</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -544,8 +544,10 @@
       <c r="F3" t="n">
         <v>314</v>
       </c>
-      <c r="G3" t="n">
-        <v>45</v>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -760,7 +762,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="G2" t="n">
         <v>45</v>
@@ -787,7 +789,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>丽水·LPJ 现实X次元动漫展</t>
+          <t>丽水·LPJ 现实X次元动漫展（取消）</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -803,8 +805,10 @@
       <c r="F3" t="n">
         <v>314</v>
       </c>
-      <c r="G3" t="n">
-        <v>45</v>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>

--- a/丽水-漫展信息.xlsx
+++ b/丽水-漫展信息.xlsx
@@ -501,10 +501,10 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G2" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -762,10 +762,10 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G2" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>

--- a/丽水-漫展信息.xlsx
+++ b/丽水-漫展信息.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -482,79 +482,38 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2024-02-14</t>
+          <t>2024.02.18</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>丽水·YA●怀旧only</t>
+          <t>丽水·LPJ 现实X次元动漫展（取消）</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>人民街567号 丽水体育中心</t>
+          <t>中东路848号(解放街交汇) 飞达国际大酒店</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2024.02.14 09:00-02.14 17:00</t>
+          <t>2024.02.18 10:00-02.18 17:00</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>125</v>
-      </c>
-      <c r="G2" t="n">
-        <v>55</v>
+        <v>314</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81032</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79437</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/LbqTNkvq1705561884633.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2024-02-18</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>丽水·LPJ 现实X次元动漫展（取消）</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>中东路848号(解放街交汇) 飞达国际大酒店</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>2024.02.18 10:00-02.18 17:00</t>
-        </is>
-      </c>
-      <c r="F3" t="n">
-        <v>314</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79437</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
         <is>
           <t>//i1.hdslb.com/bfs/openplatform/202312/ee5hLUN61702276208812.jpeg</t>
         </is>
@@ -689,7 +648,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -743,79 +702,38 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2024-02-14</t>
+          <t>2024.02.18</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>丽水·YA●怀旧only</t>
+          <t>丽水·LPJ 现实X次元动漫展（取消）</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>人民街567号 丽水体育中心</t>
+          <t>中东路848号(解放街交汇) 飞达国际大酒店</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2024.02.14 09:00-02.14 17:00</t>
+          <t>2024.02.18 10:00-02.18 17:00</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>125</v>
-      </c>
-      <c r="G2" t="n">
-        <v>55</v>
+        <v>314</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81032</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79437</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/LbqTNkvq1705561884633.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2024-02-18</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>丽水·LPJ 现实X次元动漫展（取消）</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>中东路848号(解放街交汇) 飞达国际大酒店</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>2024.02.18 10:00-02.18 17:00</t>
-        </is>
-      </c>
-      <c r="F3" t="n">
-        <v>314</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79437</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
         <is>
           <t>//i1.hdslb.com/bfs/openplatform/202312/ee5hLUN61702276208812.jpeg</t>
         </is>

--- a/丽水-漫展信息.xlsx
+++ b/丽水-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -721,7 +721,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>

--- a/丽水-漫展信息.xlsx
+++ b/丽水-漫展信息.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:I1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,49 +473,6 @@
       <c r="I1" t="inlineStr">
         <is>
           <t>Cover</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2024.02.18</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>丽水·LPJ 现实X次元动漫展（取消）</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>中东路848号(解放街交汇) 飞达国际大酒店</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>2024.02.18 10:00-02.18 17:00</t>
-        </is>
-      </c>
-      <c r="F2" t="n">
-        <v>315</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79437</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/ee5hLUN61702276208812.jpeg</t>
         </is>
       </c>
     </row>
@@ -648,7 +605,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:I1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -696,49 +653,6 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2024.02.18</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>丽水·LPJ 现实X次元动漫展（取消）</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>中东路848号(解放街交汇) 飞达国际大酒店</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>2024.02.18 10:00-02.18 17:00</t>
-        </is>
-      </c>
-      <c r="F2" t="n">
-        <v>315</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79437</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/ee5hLUN61702276208812.jpeg</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
